--- a/SCIE용/excel/31_researcher_review_checklist.xlsx
+++ b/SCIE용/excel/31_researcher_review_checklist.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="연구자 검토표" sheetId="1" r:id="rId1"/>
+    <sheet name="??? ???" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -66,7 +66,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AC55"/>
+  <dimension ref="A1:W55"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -92,12 +92,6 @@
     <col min="21" max="21" width="24" customWidth="1"/>
     <col min="22" max="22" width="24" customWidth="1"/>
     <col min="23" max="23" width="24" customWidth="1"/>
-    <col min="24" max="24" width="24" customWidth="1"/>
-    <col min="25" max="25" width="24" customWidth="1"/>
-    <col min="26" max="26" width="24" customWidth="1"/>
-    <col min="27" max="27" width="24" customWidth="1"/>
-    <col min="28" max="28" width="24" customWidth="1"/>
-    <col min="29" max="29" width="24" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -163,42 +157,42 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>자동 정확성(1-5)</t>
+          <t>1차 정확성(1-5)</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>자동 구체성(1-5)</t>
+          <t>1차 구체성(1-5)</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>자동 실습 단계 적합성(1-5)</t>
+          <t>1차 실습 단계 적합성(1-5)</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>자동 안전성(1-5)</t>
+          <t>1차 안전성(1-5)</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>자동 이해 용이성(1-5)</t>
+          <t>1차 이해 용이성(1-5)</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>자동 평균 점수</t>
+          <t>1차 평균 점수</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>자동 최종 판정</t>
+          <t>1차 최종 판정</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>자동 평가 메모</t>
+          <t>1차 평가 메모</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
@@ -208,42 +202,12 @@
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>연구자 정확성(1-5)</t>
+          <t>연구자 최종 판정(O/△/X)</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>연구자 구체성(1-5)</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>연구자 실습 단계 적합성(1-5)</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>연구자 안전성(1-5)</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>연구자 이해 용이성(1-5)</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>연구자 최종 판정(O/△/X)</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
           <t>검토 완료(Y/N)</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>수정/비고</t>
         </is>
       </c>
     </row>
@@ -341,7 +305,7 @@
       </c>
       <c r="T2" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.38; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.38; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
       <c r="U2" s="0" t="inlineStr">
@@ -349,14 +313,16 @@
           <t>해당 정보는 제공된 매뉴얼에서 찾을 수 없습니다.</t>
         </is>
       </c>
-      <c r="V2" s="0"/>
-      <c r="W2" s="0"/>
-      <c r="X2" s="0"/>
-      <c r="Y2" s="0"/>
-      <c r="Z2" s="0"/>
-      <c r="AA2" s="0"/>
-      <c r="AB2" s="0"/>
-      <c r="AC2" s="0"/>
+      <c r="V2" s="0" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="W2" s="0" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="inlineStr">
@@ -456,7 +422,7 @@
       </c>
       <c r="T3" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.47; 일치키워드=; 텍스트순위=1; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.47; 일치키워드=; 텍스트순위=1; 이미지순위=2</t>
         </is>
       </c>
       <c r="U3" s="0" t="inlineStr">
@@ -464,14 +430,16 @@
           <t>매뉴얼에 따르면, 조작기 툴 플랜지에서 직접 교시(Direct Teaching)를 활성화하기 위해 누르는 버튼은 명시되어 있지 않습니다.</t>
         </is>
       </c>
-      <c r="V3" s="0"/>
-      <c r="W3" s="0"/>
-      <c r="X3" s="0"/>
-      <c r="Y3" s="0"/>
-      <c r="Z3" s="0"/>
-      <c r="AA3" s="0"/>
-      <c r="AB3" s="0"/>
-      <c r="AC3" s="0"/>
+      <c r="V3" s="0" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="W3" s="0" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="inlineStr">
@@ -571,7 +539,7 @@
       </c>
       <c r="T4" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.55; 일치키워드=; 텍스트순위=1; 이미지순위=4</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.55; 일치키워드=; 텍스트순위=1; 이미지순위=4</t>
         </is>
       </c>
       <c r="U4" s="0" t="inlineStr">
@@ -579,14 +547,16 @@
           <t>NPN 센서를 디지털 입력 단자에 연결하는 경우,  풀업 저항을 연결해야 합니다.</t>
         </is>
       </c>
-      <c r="V4" s="0"/>
-      <c r="W4" s="0"/>
-      <c r="X4" s="0"/>
-      <c r="Y4" s="0"/>
-      <c r="Z4" s="0"/>
-      <c r="AA4" s="0"/>
-      <c r="AB4" s="0"/>
-      <c r="AC4" s="0"/>
+      <c r="V4" s="0" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="W4" s="0" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="inlineStr">
@@ -686,7 +656,7 @@
       </c>
       <c r="T5" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.43; 일치키워드=; 텍스트순위=1; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.43; 일치키워드=; 텍스트순위=1; 이미지순위=2</t>
         </is>
       </c>
       <c r="U5" s="0" t="inlineStr">
@@ -698,14 +668,16 @@
 따라서, 펜스나 라이트 커튼과 같은 보호장치를 연결할 때는 해당 장치의 작동 방식에 따라 NC 또는 NO 상태의 접점을 선택하여 사용해야 합니다.</t>
         </is>
       </c>
-      <c r="V5" s="0"/>
-      <c r="W5" s="0"/>
-      <c r="X5" s="0"/>
-      <c r="Y5" s="0"/>
-      <c r="Z5" s="0"/>
-      <c r="AA5" s="0"/>
-      <c r="AB5" s="0"/>
-      <c r="AC5" s="0"/>
+      <c r="V5" s="0" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="W5" s="0" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="inlineStr">
@@ -805,7 +777,7 @@
       </c>
       <c r="T6" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.38; 일치키워드=; 텍스트순위=1; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.38; 일치키워드=; 텍스트순위=1; 이미지순위=2</t>
         </is>
       </c>
       <c r="U6" s="0" t="inlineStr">
@@ -813,14 +785,16 @@
           <t>안전 I/O (Safety I/O) 포트에 펜스나 라이트 커튼을 연결할 때 사용하는 입력 핀 번호는  매뉴얼에서 명시되어 있지 않습니다.</t>
         </is>
       </c>
-      <c r="V6" s="0"/>
-      <c r="W6" s="0"/>
-      <c r="X6" s="0"/>
-      <c r="Y6" s="0"/>
-      <c r="Z6" s="0"/>
-      <c r="AA6" s="0"/>
-      <c r="AB6" s="0"/>
-      <c r="AC6" s="0"/>
+      <c r="V6" s="0" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="W6" s="0" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="inlineStr">
@@ -920,7 +894,7 @@
       </c>
       <c r="T7" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.43; 일치키워드=; 텍스트순위=1; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.43; 일치키워드=; 텍스트순위=1; 이미지순위=2</t>
         </is>
       </c>
       <c r="U7" s="0" t="inlineStr">
@@ -928,14 +902,16 @@
           <t>비상정지 스위치, 라이트 커튼, 안전 매트와 같은 안전기기를 연결하기 위한 Safety I/O 포트를 사용하여 펜스나 라이트 커튼을 연결할 때 사용하는 입력 핀 번호는 Protective Device Contact In: 라이트커튼, 안전매트 등 보호정지에 필요한 장치를 연결 하기에 SI1, SI2, SI3, SI4 포트를 사용합니다.</t>
         </is>
       </c>
-      <c r="V7" s="0"/>
-      <c r="W7" s="0"/>
-      <c r="X7" s="0"/>
-      <c r="Y7" s="0"/>
-      <c r="Z7" s="0"/>
-      <c r="AA7" s="0"/>
-      <c r="AB7" s="0"/>
-      <c r="AC7" s="0"/>
+      <c r="V7" s="0" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="W7" s="0" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="inlineStr">
@@ -1031,7 +1007,7 @@
       </c>
       <c r="T8" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.45; 일치키워드=; 텍스트순위=8; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.45; 일치키워드=; 텍스트순위=8; 이미지순위=</t>
         </is>
       </c>
       <c r="U8" s="0" t="inlineStr">
@@ -1043,14 +1019,16 @@
 이 화면에서 현재 로봇의 조인트 자세와 태스크 자세가 수치로 표시되어 있습니다.</t>
         </is>
       </c>
-      <c r="V8" s="0"/>
-      <c r="W8" s="0"/>
-      <c r="X8" s="0"/>
-      <c r="Y8" s="0"/>
-      <c r="Z8" s="0"/>
-      <c r="AA8" s="0"/>
-      <c r="AB8" s="0"/>
-      <c r="AC8" s="0"/>
+      <c r="V8" s="0" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="W8" s="0" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="inlineStr">
@@ -1146,7 +1124,7 @@
       </c>
       <c r="T9" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.44; 일치키워드=; 텍스트순위=8; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.44; 일치키워드=; 텍스트순위=8; 이미지순위=</t>
         </is>
       </c>
       <c r="U9" s="0" t="inlineStr">
@@ -1154,14 +1132,16 @@
           <t>PART 6.  DART-Platform 매뉴얼 항목 설명 1 로봇 자세 에서 확인 가능합니다.</t>
         </is>
       </c>
-      <c r="V9" s="0"/>
-      <c r="W9" s="0"/>
-      <c r="X9" s="0"/>
-      <c r="Y9" s="0"/>
-      <c r="Z9" s="0"/>
-      <c r="AA9" s="0"/>
-      <c r="AB9" s="0"/>
-      <c r="AC9" s="0"/>
+      <c r="V9" s="0" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="W9" s="0" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="inlineStr">
@@ -1257,7 +1237,7 @@
       </c>
       <c r="T10" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.42; 일치키워드=; 텍스트순위=8; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.42; 일치키워드=; 텍스트순위=8; 이미지순위=</t>
         </is>
       </c>
       <c r="U10" s="0" t="inlineStr">
@@ -1265,14 +1245,16 @@
           <t>조인트 자세 패널입니다.</t>
         </is>
       </c>
-      <c r="V10" s="0"/>
-      <c r="W10" s="0"/>
-      <c r="X10" s="0"/>
-      <c r="Y10" s="0"/>
-      <c r="Z10" s="0"/>
-      <c r="AA10" s="0"/>
-      <c r="AB10" s="0"/>
-      <c r="AC10" s="0"/>
+      <c r="V10" s="0" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="W10" s="0" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="inlineStr">
@@ -1372,7 +1354,7 @@
       </c>
       <c r="T11" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.41; 일치키워드=; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.41; 일치키워드=; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
       <c r="U11" s="0" t="inlineStr">
@@ -1380,14 +1362,16 @@
           <t>비상 정지 버튼을 눌렀다 해제하거나 서보 Off 버튼을 누르면 활성화됩니다.</t>
         </is>
       </c>
-      <c r="V11" s="0"/>
-      <c r="W11" s="0"/>
-      <c r="X11" s="0"/>
-      <c r="Y11" s="0"/>
-      <c r="Z11" s="0"/>
-      <c r="AA11" s="0"/>
-      <c r="AB11" s="0"/>
-      <c r="AC11" s="0"/>
+      <c r="V11" s="0" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="W11" s="0" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="inlineStr">
@@ -1487,7 +1471,7 @@
       </c>
       <c r="T12" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.45; 일치키워드=; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.45; 일치키워드=; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
       <c r="U12" s="0" t="inlineStr">
@@ -1495,14 +1479,16 @@
           <t>특이점 영역에서는 힘 제어나 순응 제어가 동작하지 않습니다.</t>
         </is>
       </c>
-      <c r="V12" s="0"/>
-      <c r="W12" s="0"/>
-      <c r="X12" s="0"/>
-      <c r="Y12" s="0"/>
-      <c r="Z12" s="0"/>
-      <c r="AA12" s="0"/>
-      <c r="AB12" s="0"/>
-      <c r="AC12" s="0"/>
+      <c r="V12" s="0" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="W12" s="0" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="inlineStr">
@@ -1598,7 +1584,7 @@
       </c>
       <c r="T13" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.47; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.47; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
       <c r="U13" s="0" t="inlineStr">
@@ -1610,14 +1596,16 @@
 위의 단계들을 통해 과거 에러 로그를 확인 및 추출할 수 있습니다.</t>
         </is>
       </c>
-      <c r="V13" s="0"/>
-      <c r="W13" s="0"/>
-      <c r="X13" s="0"/>
-      <c r="Y13" s="0"/>
-      <c r="Z13" s="0"/>
-      <c r="AA13" s="0"/>
-      <c r="AB13" s="0"/>
-      <c r="AC13" s="0"/>
+      <c r="V13" s="0" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="W13" s="0" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="inlineStr">
@@ -1713,7 +1701,7 @@
       </c>
       <c r="T14" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.49; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.49; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
       <c r="U14" s="0" t="inlineStr">
@@ -1721,14 +1709,16 @@
           <t>매뉴얼에 시스템의 과거 에러 로그를 추출하는 메뉴 경로에 대한 정보가 없습니다.</t>
         </is>
       </c>
-      <c r="V14" s="0"/>
-      <c r="W14" s="0"/>
-      <c r="X14" s="0"/>
-      <c r="Y14" s="0"/>
-      <c r="Z14" s="0"/>
-      <c r="AA14" s="0"/>
-      <c r="AB14" s="0"/>
-      <c r="AC14" s="0"/>
+      <c r="V14" s="0" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="W14" s="0" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="inlineStr">
@@ -1824,7 +1814,7 @@
       </c>
       <c r="T15" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.52; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.52; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
       <c r="U15" s="0" t="inlineStr">
@@ -1832,14 +1822,16 @@
           <t>로그 내보내기 메뉴에서 Dr.Dart-Platform 로그들을 내보낼 수 있습니다.</t>
         </is>
       </c>
-      <c r="V15" s="0"/>
-      <c r="W15" s="0"/>
-      <c r="X15" s="0"/>
-      <c r="Y15" s="0"/>
-      <c r="Z15" s="0"/>
-      <c r="AA15" s="0"/>
-      <c r="AB15" s="0"/>
-      <c r="AC15" s="0"/>
+      <c r="V15" s="0" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="W15" s="0" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="inlineStr">
@@ -1939,7 +1931,7 @@
       </c>
       <c r="T16" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.59; 일치키워드=; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.59; 일치키워드=; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
       <c r="U16" s="0" t="inlineStr">
@@ -1947,14 +1939,16 @@
           <t>케이블의 최소곡률반경 (R)은 120 mm입니다.</t>
         </is>
       </c>
-      <c r="V16" s="0"/>
-      <c r="W16" s="0"/>
-      <c r="X16" s="0"/>
-      <c r="Y16" s="0"/>
-      <c r="Z16" s="0"/>
-      <c r="AA16" s="0"/>
-      <c r="AB16" s="0"/>
-      <c r="AC16" s="0"/>
+      <c r="V16" s="0" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="W16" s="0" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="inlineStr">
@@ -2054,7 +2048,7 @@
       </c>
       <c r="T17" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.00; 일치키워드=; 텍스트순위=1; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.00; 일치키워드=; 텍스트순위=1; 이미지순위=2</t>
         </is>
       </c>
       <c r="U17" s="0" t="inlineStr">
@@ -2063,14 +2057,16 @@
 따라서, 이 질문에 대한 답변은 "manual evidence is insufficient"로 정리할 수 있습니다.</t>
         </is>
       </c>
-      <c r="V17" s="0"/>
-      <c r="W17" s="0"/>
-      <c r="X17" s="0"/>
-      <c r="Y17" s="0"/>
-      <c r="Z17" s="0"/>
-      <c r="AA17" s="0"/>
-      <c r="AB17" s="0"/>
-      <c r="AC17" s="0"/>
+      <c r="V17" s="0" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="W17" s="0" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="inlineStr">
@@ -2170,7 +2166,7 @@
       </c>
       <c r="T18" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.59; 일치키워드=; 텍스트순위=1; 이미지순위=8</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.59; 일치키워드=; 텍스트순위=1; 이미지순위=8</t>
         </is>
       </c>
       <c r="U18" s="0" t="inlineStr">
@@ -2178,14 +2174,16 @@
           <t>조인트 모션입니다.</t>
         </is>
       </c>
-      <c r="V18" s="0"/>
-      <c r="W18" s="0"/>
-      <c r="X18" s="0"/>
-      <c r="Y18" s="0"/>
-      <c r="Z18" s="0"/>
-      <c r="AA18" s="0"/>
-      <c r="AB18" s="0"/>
-      <c r="AC18" s="0"/>
+      <c r="V18" s="0" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="W18" s="0" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="0" t="inlineStr">
@@ -2285,7 +2283,7 @@
       </c>
       <c r="T19" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.56; 일치키워드=; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.56; 일치키워드=; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
       <c r="U19" s="0" t="inlineStr">
@@ -2293,14 +2291,16 @@
           <t>Z 축 방향 오프셋만 적용하려면 TCP 설정 화면에서 **Z** 항목에 값을 입력해야 합니다.</t>
         </is>
       </c>
-      <c r="V19" s="0"/>
-      <c r="W19" s="0"/>
-      <c r="X19" s="0"/>
-      <c r="Y19" s="0"/>
-      <c r="Z19" s="0"/>
-      <c r="AA19" s="0"/>
-      <c r="AB19" s="0"/>
-      <c r="AC19" s="0"/>
+      <c r="V19" s="0" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="W19" s="0" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="0" t="inlineStr">
@@ -2400,7 +2400,7 @@
       </c>
       <c r="T20" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.46; 일치키워드=; 텍스트순위=1; 이미지순위=4</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.46; 일치키워드=; 텍스트순위=1; 이미지순위=4</t>
         </is>
       </c>
       <c r="U20" s="0" t="inlineStr">
@@ -2408,14 +2408,16 @@
           <t>안전 영역(Zone) 설정 시 선택할 수 있는 3D 도형 모양은 총 5 가지입니다. 이들은 Cuboid, Cylinder, Sphere, Tilted Cuboid, Multi-plane Box 입니다.</t>
         </is>
       </c>
-      <c r="V20" s="0"/>
-      <c r="W20" s="0"/>
-      <c r="X20" s="0"/>
-      <c r="Y20" s="0"/>
-      <c r="Z20" s="0"/>
-      <c r="AA20" s="0"/>
-      <c r="AB20" s="0"/>
-      <c r="AC20" s="0"/>
+      <c r="V20" s="0" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="W20" s="0" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="inlineStr">
@@ -2511,7 +2513,7 @@
       </c>
       <c r="T21" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.36; 일치키워드=; 텍스트순위=10; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.36; 일치키워드=; 텍스트순위=10; 이미지순위=</t>
         </is>
       </c>
       <c r="U21" s="0" t="inlineStr">
@@ -2519,14 +2521,16 @@
           <t>두산로보틱스의 프로그래밍 모듈 명칭은 명시되어 있지 않습니다. 하지만, 제공된 정보에서 SubTask 명령어와 CallSubTask 명령어를 사용하여 로봇 동작을 구성할 수 있음을 알 수 있습니다. 이는 프로그램 명령어들을 조립하여 로봇의 동작을 설정하는 과정에 해당합니다.</t>
         </is>
       </c>
-      <c r="V21" s="0"/>
-      <c r="W21" s="0"/>
-      <c r="X21" s="0"/>
-      <c r="Y21" s="0"/>
-      <c r="Z21" s="0"/>
-      <c r="AA21" s="0"/>
-      <c r="AB21" s="0"/>
-      <c r="AC21" s="0"/>
+      <c r="V21" s="0" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="W21" s="0" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="inlineStr">
@@ -2622,7 +2626,7 @@
       </c>
       <c r="T22" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.32; 일치키워드=; 텍스트순위=10; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.32; 일치키워드=; 텍스트순위=10; 이미지순위=</t>
         </is>
       </c>
       <c r="U22" s="0" t="inlineStr">
@@ -2630,14 +2634,16 @@
           <t>제공된 문서에는 두산로보틱스의 프로그래밍 모듈 명칭에 대한 정보가 없습니다.</t>
         </is>
       </c>
-      <c r="V22" s="0"/>
-      <c r="W22" s="0"/>
-      <c r="X22" s="0"/>
-      <c r="Y22" s="0"/>
-      <c r="Z22" s="0"/>
-      <c r="AA22" s="0"/>
-      <c r="AB22" s="0"/>
-      <c r="AC22" s="0"/>
+      <c r="V22" s="0" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="W22" s="0" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="inlineStr">
@@ -2733,7 +2739,7 @@
       </c>
       <c r="T23" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.42; 일치키워드=; 텍스트순위=10; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.42; 일치키워드=; 텍스트순위=10; 이미지순위=</t>
         </is>
       </c>
       <c r="U23" s="0" t="inlineStr">
@@ -2741,14 +2747,16 @@
           <t>SubTask 명령어와 CallSubTask 명령어를 사용하여 다양한 프로그램 명령어를 조립하여 로봇 동작을 구성할 수 있습니다.</t>
         </is>
       </c>
-      <c r="V23" s="0"/>
-      <c r="W23" s="0"/>
-      <c r="X23" s="0"/>
-      <c r="Y23" s="0"/>
-      <c r="Z23" s="0"/>
-      <c r="AA23" s="0"/>
-      <c r="AB23" s="0"/>
-      <c r="AC23" s="0"/>
+      <c r="V23" s="0" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="W23" s="0" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="0" t="inlineStr">
@@ -2844,7 +2852,7 @@
       </c>
       <c r="T24" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.52; 일치키워드=; 텍스트순위=3; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.52; 일치키워드=; 텍스트순위=3; 이미지순위=</t>
         </is>
       </c>
       <c r="U24" s="0" t="inlineStr">
@@ -2852,14 +2860,16 @@
           <t>Move L입니다. 이 모션 명령어를 사용하면 로봇의 목표 위치까지 직선을 따라 가장 빠르게 이동할 수 있습니다.</t>
         </is>
       </c>
-      <c r="V24" s="0"/>
-      <c r="W24" s="0"/>
-      <c r="X24" s="0"/>
-      <c r="Y24" s="0"/>
-      <c r="Z24" s="0"/>
-      <c r="AA24" s="0"/>
-      <c r="AB24" s="0"/>
-      <c r="AC24" s="0"/>
+      <c r="V24" s="0" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="W24" s="0" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="inlineStr">
@@ -2959,7 +2969,7 @@
       </c>
       <c r="T25" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.42; 일치키워드=; 텍스트순위=1; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.42; 일치키워드=; 텍스트순위=1; 이미지순위=2</t>
         </is>
       </c>
       <c r="U25" s="0" t="inlineStr">
@@ -2967,14 +2977,16 @@
           <t>확장자에 대한 명시는 매뉴얼에서 확인되지 않았습니다. 따라서, 이 질문에 대해 정확히 답하기에는 매뉴얼 내 정보가 부족합니다.</t>
         </is>
       </c>
-      <c r="V25" s="0"/>
-      <c r="W25" s="0"/>
-      <c r="X25" s="0"/>
-      <c r="Y25" s="0"/>
-      <c r="Z25" s="0"/>
-      <c r="AA25" s="0"/>
-      <c r="AB25" s="0"/>
-      <c r="AC25" s="0"/>
+      <c r="V25" s="0" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="W25" s="0" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="inlineStr">
@@ -3070,7 +3082,7 @@
       </c>
       <c r="T26" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.29; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.29; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
       <c r="U26" s="0" t="inlineStr">
@@ -3078,14 +3090,16 @@
           <t>제공된 문서에는 로봇 큐브 모듈 케이블 결합 시 방수 등급 강화를 위한 특정 부품에 대한 정보가 없습니다.</t>
         </is>
       </c>
-      <c r="V26" s="0"/>
-      <c r="W26" s="0"/>
-      <c r="X26" s="0"/>
-      <c r="Y26" s="0"/>
-      <c r="Z26" s="0"/>
-      <c r="AA26" s="0"/>
-      <c r="AB26" s="0"/>
-      <c r="AC26" s="0"/>
+      <c r="V26" s="0" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="W26" s="0" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="0" t="inlineStr">
@@ -3185,7 +3199,7 @@
       </c>
       <c r="T27" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.41; 일치키워드=; 텍스트순위=1; 이미지순위=3</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.41; 일치키워드=; 텍스트순위=1; 이미지순위=3</t>
         </is>
       </c>
       <c r="U27" s="0" t="inlineStr">
@@ -3193,14 +3207,16 @@
           <t>매뉴얼 내용에는 티치펜던트에 위치한 USB 포트의 용도에 대한 정보가 없습니다.</t>
         </is>
       </c>
-      <c r="V27" s="0"/>
-      <c r="W27" s="0"/>
-      <c r="X27" s="0"/>
-      <c r="Y27" s="0"/>
-      <c r="Z27" s="0"/>
-      <c r="AA27" s="0"/>
-      <c r="AB27" s="0"/>
-      <c r="AC27" s="0"/>
+      <c r="V27" s="0" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="W27" s="0" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="0" t="inlineStr">
@@ -3300,7 +3316,7 @@
       </c>
       <c r="T28" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.45; 일치키워드=; 텍스트순위=7; 이미지순위=6</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.45; 일치키워드=; 텍스트순위=7; 이미지순위=6</t>
         </is>
       </c>
       <c r="U28" s="0" t="inlineStr">
@@ -3309,14 +3325,16 @@
 따라서, "매뉴얼证据不足"라고 답변하겠습니다.</t>
         </is>
       </c>
-      <c r="V28" s="0"/>
-      <c r="W28" s="0"/>
-      <c r="X28" s="0"/>
-      <c r="Y28" s="0"/>
-      <c r="Z28" s="0"/>
-      <c r="AA28" s="0"/>
-      <c r="AB28" s="0"/>
-      <c r="AC28" s="0"/>
+      <c r="V28" s="0" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="W28" s="0" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="0" t="inlineStr">
@@ -3416,7 +3434,7 @@
       </c>
       <c r="T29" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.37; 일치키워드=; 텍스트순위=7; 이미지순위=6</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.37; 일치키워드=; 텍스트순위=7; 이미지순위=6</t>
         </is>
       </c>
       <c r="U29" s="0" t="inlineStr">
@@ -3424,14 +3442,16 @@
           <t>제공된 설명서는 로봇이 프로그램 시작점으로 기본 복귀하는 기능에 대한 정보를 제공하지 않습니다. 따라서, 해당 질문에 답변할 수 없습니다.</t>
         </is>
       </c>
-      <c r="V29" s="0"/>
-      <c r="W29" s="0"/>
-      <c r="X29" s="0"/>
-      <c r="Y29" s="0"/>
-      <c r="Z29" s="0"/>
-      <c r="AA29" s="0"/>
-      <c r="AB29" s="0"/>
-      <c r="AC29" s="0"/>
+      <c r="V29" s="0" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="W29" s="0" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="0" t="inlineStr">
@@ -3531,7 +3551,7 @@
       </c>
       <c r="T30" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.41; 일치키워드=; 텍스트순위=7; 이미지순위=6</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.41; 일치키워드=; 텍스트순위=7; 이미지순위=6</t>
         </is>
       </c>
       <c r="U30" s="0" t="inlineStr">
@@ -3539,14 +3559,16 @@
           <t>해당 정보는 제공된 매뉴얼에 없습니다.</t>
         </is>
       </c>
-      <c r="V30" s="0"/>
-      <c r="W30" s="0"/>
-      <c r="X30" s="0"/>
-      <c r="Y30" s="0"/>
-      <c r="Z30" s="0"/>
-      <c r="AA30" s="0"/>
-      <c r="AB30" s="0"/>
-      <c r="AC30" s="0"/>
+      <c r="V30" s="0" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="W30" s="0" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="0" t="inlineStr">
@@ -3646,7 +3668,7 @@
       </c>
       <c r="T31" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.34; 일치키워드=; 텍스트순위=1; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.34; 일치키워드=; 텍스트순위=1; 이미지순위=2</t>
         </is>
       </c>
       <c r="U31" s="0" t="inlineStr">
@@ -3654,14 +3676,16 @@
           <t>제공된 설명서에는 Configurable 디지털 I/O 전원을 내부 전원과 분리하기 위한 점퍼선 결선에 대한 정보가 없습니다.</t>
         </is>
       </c>
-      <c r="V31" s="0"/>
-      <c r="W31" s="0"/>
-      <c r="X31" s="0"/>
-      <c r="Y31" s="0"/>
-      <c r="Z31" s="0"/>
-      <c r="AA31" s="0"/>
-      <c r="AB31" s="0"/>
-      <c r="AC31" s="0"/>
+      <c r="V31" s="0" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="W31" s="0" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="0" t="inlineStr">
@@ -3761,7 +3785,7 @@
       </c>
       <c r="T32" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.44; 일치키워드=; 텍스트순위=2; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.44; 일치키워드=; 텍스트순위=2; 이미지순위=2</t>
         </is>
       </c>
       <c r="U32" s="0" t="inlineStr">
@@ -3769,14 +3793,16 @@
           <t>전기적 지면 연결입니다.</t>
         </is>
       </c>
-      <c r="V32" s="0"/>
-      <c r="W32" s="0"/>
-      <c r="X32" s="0"/>
-      <c r="Y32" s="0"/>
-      <c r="Z32" s="0"/>
-      <c r="AA32" s="0"/>
-      <c r="AB32" s="0"/>
-      <c r="AC32" s="0"/>
+      <c r="V32" s="0" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="W32" s="0" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="0" t="inlineStr">
@@ -3876,7 +3902,7 @@
       </c>
       <c r="T33" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.24; 일치키워드=; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.24; 일치키워드=; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
       <c r="U33" s="0" t="inlineStr">
@@ -3884,14 +3910,16 @@
           <t>매니龃哌哌哌哌哌哌哌哌哌哌哌哌哌哌哌哌哌哌哌哌哌哌哌哌哌哌哌哌哌哌哌</t>
         </is>
       </c>
-      <c r="V33" s="0"/>
-      <c r="W33" s="0"/>
-      <c r="X33" s="0"/>
-      <c r="Y33" s="0"/>
-      <c r="Z33" s="0"/>
-      <c r="AA33" s="0"/>
-      <c r="AB33" s="0"/>
-      <c r="AC33" s="0"/>
+      <c r="V33" s="0" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="W33" s="0" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="0" t="inlineStr">
@@ -3991,7 +4019,7 @@
       </c>
       <c r="T34" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.59; 일치키워드=; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.59; 일치키워드=; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
       <c r="U34" s="0" t="inlineStr">
@@ -3999,14 +4027,16 @@
           <t>TBSI (T) 단자입니다.</t>
         </is>
       </c>
-      <c r="V34" s="0"/>
-      <c r="W34" s="0"/>
-      <c r="X34" s="0"/>
-      <c r="Y34" s="0"/>
-      <c r="Z34" s="0"/>
-      <c r="AA34" s="0"/>
-      <c r="AB34" s="0"/>
-      <c r="AC34" s="0"/>
+      <c r="V34" s="0" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="W34" s="0" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="0" t="inlineStr">
@@ -4106,7 +4136,7 @@
       </c>
       <c r="T35" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.53; 일치키워드=; 텍스트순위=4; 이미지순위=4</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.53; 일치키워드=; 텍스트순위=4; 이미지순위=4</t>
         </is>
       </c>
       <c r="U35" s="0" t="inlineStr">
@@ -4114,14 +4144,16 @@
           <t>두 점을 사용하는 원기둥형태의 공간 제한 구역에서 입력해야 하는 주요 위치 항목은 반지름 거리의 점, 윗면의 한 점, 밑면의 한 점입니다.</t>
         </is>
       </c>
-      <c r="V35" s="0"/>
-      <c r="W35" s="0"/>
-      <c r="X35" s="0"/>
-      <c r="Y35" s="0"/>
-      <c r="Z35" s="0"/>
-      <c r="AA35" s="0"/>
-      <c r="AB35" s="0"/>
-      <c r="AC35" s="0"/>
+      <c r="V35" s="0" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="W35" s="0" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="0" t="inlineStr">
@@ -4217,7 +4249,7 @@
       </c>
       <c r="T36" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.20; 의미유사도=0.53; 일치키워드=고장; 텍스트순위=2; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.20; 의미유사도=0.53; 일치키워드=고장; 텍스트순위=2; 이미지순위=</t>
         </is>
       </c>
       <c r="U36" s="0" t="inlineStr">
@@ -4228,14 +4260,16 @@
 따라서 이러한 개조나 연장은 절대 금지되어 있으며, 안전을 위해 공식적으로 승인된 방법으로만 케이블을 관리해야 합니다.</t>
         </is>
       </c>
-      <c r="V36" s="0"/>
-      <c r="W36" s="0"/>
-      <c r="X36" s="0"/>
-      <c r="Y36" s="0"/>
-      <c r="Z36" s="0"/>
-      <c r="AA36" s="0"/>
-      <c r="AB36" s="0"/>
-      <c r="AC36" s="0"/>
+      <c r="V36" s="0" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="W36" s="0" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="0" t="inlineStr">
@@ -4335,7 +4369,7 @@
       </c>
       <c r="T37" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.14; 의미유사도=0.66; 일치키워드=권장; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.14; 의미유사도=0.66; 일치키워드=권장; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
       <c r="U37" s="0" t="inlineStr">
@@ -4343,14 +4377,16 @@
           <t>로봇 베이스를 바닥에 고정할 때 사용하는 볼트의 권장 규격은 M8이며, 체결 토크는 20Nm으로 권장됩니다.</t>
         </is>
       </c>
-      <c r="V37" s="0"/>
-      <c r="W37" s="0"/>
-      <c r="X37" s="0"/>
-      <c r="Y37" s="0"/>
-      <c r="Z37" s="0"/>
-      <c r="AA37" s="0"/>
-      <c r="AB37" s="0"/>
-      <c r="AC37" s="0"/>
+      <c r="V37" s="0" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="W37" s="0" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="0" t="inlineStr">
@@ -4450,7 +4486,7 @@
       </c>
       <c r="T38" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.62; 일치키워드=우측; 텍스트순위=1; 이미지순위=6</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.62; 일치키워드=우측; 텍스트순위=1; 이미지순위=6</t>
         </is>
       </c>
       <c r="U38" s="0" t="inlineStr">
@@ -4458,14 +4494,16 @@
           <t>비상 상황 발생 시 즉각적인 조치를 위해 티치펜던트 우측 상단에 위치한 비상 정지 버튼을 눌러 시스템을 즉시 정지할 수 있습니다.</t>
         </is>
       </c>
-      <c r="V38" s="0"/>
-      <c r="W38" s="0"/>
-      <c r="X38" s="0"/>
-      <c r="Y38" s="0"/>
-      <c r="Z38" s="0"/>
-      <c r="AA38" s="0"/>
-      <c r="AB38" s="0"/>
-      <c r="AC38" s="0"/>
+      <c r="V38" s="0" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="W38" s="0" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="0" t="inlineStr">
@@ -4565,7 +4603,7 @@
       </c>
       <c r="T39" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.48; 일치키워드=; 텍스트순위=1; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.48; 일치키워드=; 텍스트순위=1; 이미지순위=2</t>
         </is>
       </c>
       <c r="U39" s="0" t="inlineStr">
@@ -4573,14 +4611,16 @@
           <t>협동로봇의 직접 교시(Direct Teaching)를 활성화하기 위해 조작기 툴 플랜지에서 핸드가이드 버튼을 누르면 됩니다. 이 버튼을 눌렀을 때, 자율이동 모드(Freedrive)로 로봇을 움직일 수 있습니다.</t>
         </is>
       </c>
-      <c r="V39" s="0"/>
-      <c r="W39" s="0"/>
-      <c r="X39" s="0"/>
-      <c r="Y39" s="0"/>
-      <c r="Z39" s="0"/>
-      <c r="AA39" s="0"/>
-      <c r="AB39" s="0"/>
-      <c r="AC39" s="0"/>
+      <c r="V39" s="0" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="W39" s="0" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="0" t="inlineStr">
@@ -4680,7 +4720,7 @@
       </c>
       <c r="T40" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.17; 의미유사도=0.44; 일치키워드=연결; 텍스트순위=1; 이미지순위=4</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.17; 의미유사도=0.44; 일치키워드=연결; 텍스트순위=1; 이미지순위=4</t>
         </is>
       </c>
       <c r="U40" s="0" t="inlineStr">
@@ -4692,14 +4732,16 @@
 위의 사항들을 준수하여 배선을 진행하시면, NPN 타입 센서가 제어기의 디지털 입력 단자와 정상적으로 연결될 수 있습니다.</t>
         </is>
       </c>
-      <c r="V40" s="0"/>
-      <c r="W40" s="0"/>
-      <c r="X40" s="0"/>
-      <c r="Y40" s="0"/>
-      <c r="Z40" s="0"/>
-      <c r="AA40" s="0"/>
-      <c r="AB40" s="0"/>
-      <c r="AC40" s="0"/>
+      <c r="V40" s="0" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="W40" s="0" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="0" t="inlineStr">
@@ -4799,7 +4841,7 @@
       </c>
       <c r="T41" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.55; 일치키워드=; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.55; 일치키워드=; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
       <c r="U41" s="0" t="inlineStr">
@@ -4807,14 +4849,16 @@
           <t>TCP 설정 화면에서 Z축 방향의 오프셋만 적용하려면 [Z] 항목에 값 100을 입력해야 합니다. 다른 [A], [B], [C] 항목은 0으로 두어야 합니다. 예를 들어, [X, Y, Z, A, B, C] = [0, 0, 100, 0, 0, 0] 형식으로 설정하면 됩니다.</t>
         </is>
       </c>
-      <c r="V41" s="0"/>
-      <c r="W41" s="0"/>
-      <c r="X41" s="0"/>
-      <c r="Y41" s="0"/>
-      <c r="Z41" s="0"/>
-      <c r="AA41" s="0"/>
-      <c r="AB41" s="0"/>
-      <c r="AC41" s="0"/>
+      <c r="V41" s="0" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="W41" s="0" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="0" t="inlineStr">
@@ -4914,7 +4958,7 @@
       </c>
       <c r="T42" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.51; 일치키워드=; 텍스트순위=2; 이미지순위=7</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.51; 일치키워드=; 텍스트순위=2; 이미지순위=7</t>
         </is>
       </c>
       <c r="U42" s="0" t="inlineStr">
@@ -4922,14 +4966,16 @@
           <t>직선으로 이동하도록 강제하는 모션 명령어는 Move L입니다. 이 명령어는 목표하는 작업 공간 좌표로 직선을 따라 로봇을 이동시키기 위해 사용됩니다.</t>
         </is>
       </c>
-      <c r="V42" s="0"/>
-      <c r="W42" s="0"/>
-      <c r="X42" s="0"/>
-      <c r="Y42" s="0"/>
-      <c r="Z42" s="0"/>
-      <c r="AA42" s="0"/>
-      <c r="AB42" s="0"/>
-      <c r="AC42" s="0"/>
+      <c r="V42" s="0" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="W42" s="0" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="0" t="inlineStr">
@@ -5025,7 +5071,7 @@
       </c>
       <c r="T43" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.51; 일치키워드=; 텍스트순위=3; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.51; 일치키워드=; 텍스트순위=3; 이미지순위=</t>
         </is>
       </c>
       <c r="U43" s="0" t="inlineStr">
@@ -5033,14 +5079,16 @@
           <t>조인트 각도를 기준으로 목표 위치까지 가장 빠른 경로로 이동하는 모션 명령어는 `Move JX` 입니다. 이 명령어는 목표하는 작업 공간 좌표 및 관절 형태로 로봇을 이동시키는데 사용되며, 이는 가장 효율적인 경로를 통해 목적지까지 이동할 수 있게 해줍니다.</t>
         </is>
       </c>
-      <c r="V43" s="0"/>
-      <c r="W43" s="0"/>
-      <c r="X43" s="0"/>
-      <c r="Y43" s="0"/>
-      <c r="Z43" s="0"/>
-      <c r="AA43" s="0"/>
-      <c r="AB43" s="0"/>
-      <c r="AC43" s="0"/>
+      <c r="V43" s="0" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="W43" s="0" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="0" t="inlineStr">
@@ -5140,7 +5188,7 @@
       </c>
       <c r="T44" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.12; 의미유사도=0.58; 일치키워드=표시된; 텍스트순위=1; 이미지순위=5</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.12; 의미유사도=0.58; 일치키워드=표시된; 텍스트순위=1; 이미지순위=5</t>
         </is>
       </c>
       <c r="U44" s="0" t="inlineStr">
@@ -5148,14 +5196,16 @@
           <t>로봇을 설치 장소로 옮길 때 들어올려야 하는 부분은 음영 표시된 부분입니다. 안전 사고를 예방하기 위해 해당 지역 또는 국가의 중량 운반 작업 기준을 확인하고, 지침을 준수하여 운반해야 합니다.</t>
         </is>
       </c>
-      <c r="V44" s="0"/>
-      <c r="W44" s="0"/>
-      <c r="X44" s="0"/>
-      <c r="Y44" s="0"/>
-      <c r="Z44" s="0"/>
-      <c r="AA44" s="0"/>
-      <c r="AB44" s="0"/>
-      <c r="AC44" s="0"/>
+      <c r="V44" s="0" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="W44" s="0" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="0" t="inlineStr">
@@ -5255,7 +5305,7 @@
       </c>
       <c r="T45" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.11; 의미유사도=0.68; 일치키워드=볼트; 텍스트순위=1; 이미지순위=2</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.11; 의미유사도=0.68; 일치키워드=볼트; 텍스트순위=1; 이미지순위=2</t>
         </is>
       </c>
       <c r="U45" s="0" t="inlineStr">
@@ -5263,14 +5313,16 @@
           <t>툴을 툴 플랜지에 고정할 때 사용하는 볼트 수는 4개이며, 권장 체결 토크는 9 Nm입니다.</t>
         </is>
       </c>
-      <c r="V45" s="0"/>
-      <c r="W45" s="0"/>
-      <c r="X45" s="0"/>
-      <c r="Y45" s="0"/>
-      <c r="Z45" s="0"/>
-      <c r="AA45" s="0"/>
-      <c r="AB45" s="0"/>
-      <c r="AC45" s="0"/>
+      <c r="V45" s="0" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="W45" s="0" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="0" t="inlineStr">
@@ -5370,7 +5422,7 @@
       </c>
       <c r="T46" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.20; 의미유사도=0.69; 일치키워드=입력받을; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.20; 의미유사도=0.69; 일치키워드=입력받을; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
       <c r="U46" s="0" t="inlineStr">
@@ -5378,14 +5430,16 @@
           <t>컨트롤러의 외부 엔코더 입력 단자 TBEN은 A, B, Z 상을 입력받을 수 있습니다.</t>
         </is>
       </c>
-      <c r="V46" s="0"/>
-      <c r="W46" s="0"/>
-      <c r="X46" s="0"/>
-      <c r="Y46" s="0"/>
-      <c r="Z46" s="0"/>
-      <c r="AA46" s="0"/>
-      <c r="AB46" s="0"/>
-      <c r="AC46" s="0"/>
+      <c r="V46" s="0" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="W46" s="0" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="0" t="inlineStr">
@@ -5485,7 +5539,7 @@
       </c>
       <c r="T47" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.50; 일치키워드=; 텍스트순위=1; 이미지순위=1</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.50; 일치키워드=; 텍스트순위=1; 이미지순위=1</t>
         </is>
       </c>
       <c r="U47" s="0" t="inlineStr">
@@ -5493,14 +5547,16 @@
           <t>테스트 펄스가 포함된 안전신호를 연결할 수 있는 Safety Controller의 전용 안전 입력 단자는 TBSI 단자입니다. 각 포트는 최대 1ms의 테스트 펄스를 20ms 당 최대 1개까지 허용하며, Low active 신호에만 테스트 펄스가 허용됩니다.</t>
         </is>
       </c>
-      <c r="V47" s="0"/>
-      <c r="W47" s="0"/>
-      <c r="X47" s="0"/>
-      <c r="Y47" s="0"/>
-      <c r="Z47" s="0"/>
-      <c r="AA47" s="0"/>
-      <c r="AB47" s="0"/>
-      <c r="AC47" s="0"/>
+      <c r="V47" s="0" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="W47" s="0" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="0" t="inlineStr">
@@ -5596,7 +5652,7 @@
       </c>
       <c r="T48" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.64; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.64; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
       <c r="U48" s="0" t="inlineStr">
@@ -5604,14 +5660,16 @@
           <t>구 형태의 안전 영역을 설정할 때 중심 위치는 X, Y, Z 좌표값으로 입력합니다. 이는 구의 중심점의 위치를 정의하기 위함입니다.</t>
         </is>
       </c>
-      <c r="V48" s="0"/>
-      <c r="W48" s="0"/>
-      <c r="X48" s="0"/>
-      <c r="Y48" s="0"/>
-      <c r="Z48" s="0"/>
-      <c r="AA48" s="0"/>
-      <c r="AB48" s="0"/>
-      <c r="AC48" s="0"/>
+      <c r="V48" s="0" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="W48" s="0" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="0" t="inlineStr">
@@ -5711,7 +5769,7 @@
       </c>
       <c r="T49" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.56; 일치키워드=; 텍스트순위=4; 이미지순위=4</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.56; 일치키워드=; 텍스트순위=4; 이미지순위=4</t>
         </is>
       </c>
       <c r="U49" s="0" t="inlineStr">
@@ -5729,14 +5787,16 @@
 이러한 위치 항목을 입력하고 포즈 저장 버튼을 탭하여 공간 제한 구역을 설정할 수 있습니다.</t>
         </is>
       </c>
-      <c r="V49" s="0"/>
-      <c r="W49" s="0"/>
-      <c r="X49" s="0"/>
-      <c r="Y49" s="0"/>
-      <c r="Z49" s="0"/>
-      <c r="AA49" s="0"/>
-      <c r="AB49" s="0"/>
-      <c r="AC49" s="0"/>
+      <c r="V49" s="0" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="W49" s="0" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="0" t="inlineStr">
@@ -5836,7 +5896,7 @@
       </c>
       <c r="T50" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.55; 일치키워드=누전차단기; 텍스트순위=1; 이미지순위=5</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.50; 의미유사도=0.55; 일치키워드=누전차단기; 텍스트순위=1; 이미지순위=5</t>
         </is>
       </c>
       <c r="U50" s="0" t="inlineStr">
@@ -5847,14 +5907,16 @@
 이 외에도 전원 케이블은 임의로 개조하거나 연장하지 않고, 원래 제공된 올바른 전선을 사용해야 하며, 모든 케이블이 연결되어 있는지 확인한 후에 제어기에 전원을 공급해야 합니다.</t>
         </is>
       </c>
-      <c r="V50" s="0"/>
-      <c r="W50" s="0"/>
-      <c r="X50" s="0"/>
-      <c r="Y50" s="0"/>
-      <c r="Z50" s="0"/>
-      <c r="AA50" s="0"/>
-      <c r="AB50" s="0"/>
-      <c r="AC50" s="0"/>
+      <c r="V50" s="0" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="W50" s="0" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="0" t="inlineStr">
@@ -5954,7 +6016,7 @@
       </c>
       <c r="T51" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.45; 일치키워드=시간; 텍스트순위=4; 이미지순위=5</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.25; 의미유사도=0.45; 일치키워드=시간; 텍스트순위=4; 이미지순위=5</t>
         </is>
       </c>
       <c r="U51" s="0" t="inlineStr">
@@ -5962,14 +6024,16 @@
           <t>매뉴얼에 따르면, 로봇 시스템의 시간 기능을 확인할 수 있는 곳은 대시보드 메뉴 구성 항목 중 '전체 시간' 항목에서 확인할 수 있습니다. 이 항목은 전체 시간 태스크가 실행된 시간을 표시합니다.</t>
         </is>
       </c>
-      <c r="V51" s="0"/>
-      <c r="W51" s="0"/>
-      <c r="X51" s="0"/>
-      <c r="Y51" s="0"/>
-      <c r="Z51" s="0"/>
-      <c r="AA51" s="0"/>
-      <c r="AB51" s="0"/>
-      <c r="AC51" s="0"/>
+      <c r="V51" s="0" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="W51" s="0" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="0" t="inlineStr">
@@ -6069,7 +6133,7 @@
       </c>
       <c r="T52" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.33; 의미유사도=0.62; 일치키워드=내보내기,태스크; 텍스트순위=1; 이미지순위=3</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.33; 의미유사도=0.62; 일치키워드=내보내기,태스크; 텍스트순위=1; 이미지순위=3</t>
         </is>
       </c>
       <c r="U52" s="0" t="inlineStr">
@@ -6077,14 +6141,16 @@
           <t>티치펜던트에 위치한 USB 포트의 주된 용도는 로봇 동작 중 발생하는 로그를 USB 저장매체에 저장하거나 태스크 내보내기, 가져오기를 수행할 수 있게 하는 것입니다.</t>
         </is>
       </c>
-      <c r="V52" s="0"/>
-      <c r="W52" s="0"/>
-      <c r="X52" s="0"/>
-      <c r="Y52" s="0"/>
-      <c r="Z52" s="0"/>
-      <c r="AA52" s="0"/>
-      <c r="AB52" s="0"/>
-      <c r="AC52" s="0"/>
+      <c r="V52" s="0" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="W52" s="0" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="0" t="inlineStr">
@@ -6180,7 +6246,7 @@
       </c>
       <c r="T53" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.45; 일치키워드=; 텍스트순위=8; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.45; 일치키워드=; 텍스트순위=8; 이미지순위=</t>
         </is>
       </c>
       <c r="U53" s="0" t="inlineStr">
@@ -6192,14 +6258,16 @@
 이 화면에서 현재 로봇의 조인트 자세와 태스크 자세가 수치로 표시되어 있습니다.</t>
         </is>
       </c>
-      <c r="V53" s="0"/>
-      <c r="W53" s="0"/>
-      <c r="X53" s="0"/>
-      <c r="Y53" s="0"/>
-      <c r="Z53" s="0"/>
-      <c r="AA53" s="0"/>
-      <c r="AB53" s="0"/>
-      <c r="AC53" s="0"/>
+      <c r="V53" s="0" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="W53" s="0" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="0" t="inlineStr">
@@ -6295,7 +6363,7 @@
       </c>
       <c r="T54" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.47; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=0.00; 의미유사도=0.47; 일치키워드=; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
       <c r="U54" s="0" t="inlineStr">
@@ -6307,14 +6375,16 @@
 위의 단계들을 통해 과거 에러 로그를 확인 및 추출할 수 있습니다.</t>
         </is>
       </c>
-      <c r="V54" s="0"/>
-      <c r="W54" s="0"/>
-      <c r="X54" s="0"/>
-      <c r="Y54" s="0"/>
-      <c r="Z54" s="0"/>
-      <c r="AA54" s="0"/>
-      <c r="AB54" s="0"/>
-      <c r="AC54" s="0"/>
+      <c r="V54" s="0" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="W54" s="0" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="0" t="inlineStr">
@@ -6410,7 +6480,7 @@
       </c>
       <c r="T55" s="0" t="inlineStr">
         <is>
-          <t>자동 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.62; 일치키워드=grommet,그로밋; 텍스트순위=1; 이미지순위=</t>
+          <t>rubric 기반 1차 평가; 정답키워드일치율=1.00; 의미유사도=0.62; 일치키워드=grommet,그로밋; 텍스트순위=1; 이미지순위=</t>
         </is>
       </c>
       <c r="U55" s="0" t="inlineStr">
@@ -6418,16 +6488,18 @@
           <t>Manuals에 따르면, 로봇 큐브모듈의 프레임 커버 분해 후 케이블을 연결할 때 그로밋 (Grommet)을 결합하여 방수 등급을 강화해야 합니다. 따라서, 케이블에 결합해야 하는 부품은 그로밋 (Grommet)입니다.</t>
         </is>
       </c>
-      <c r="V55" s="0"/>
-      <c r="W55" s="0"/>
-      <c r="X55" s="0"/>
-      <c r="Y55" s="0"/>
-      <c r="Z55" s="0"/>
-      <c r="AA55" s="0"/>
-      <c r="AB55" s="0"/>
-      <c r="AC55" s="0"/>
+      <c r="V55" s="0" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="W55" s="0" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AC55"/>
+  <autoFilter ref="A1:W55"/>
 </worksheet>
 </file>